--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/1909-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/1909-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{298E156B-CD28-48D6-8CA7-360568D9FA0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ECD58412-2BA7-4802-BAEA-46A8652B1876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{98F66D75-4655-4E54-A9D9-5AFB71F8FEB4}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{97B7E895-91DB-4EC5-A534-F1E5C51CF189}"/>
   </bookViews>
   <sheets>
     <sheet name="1909-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1481,25 +1481,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A1B02B9-F0B4-4C46-9C9B-CD6E6C6BA9A5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C4135B2-115C-4E15-A181-4A4ACB946E43}">
   <dimension ref="A1:R66"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1527,7 +1527,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1557,7 +1557,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1603,7 +1603,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1653,7 +1653,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="39">
         <v>2025</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2024</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="39">
         <v>2023</v>
       </c>
@@ -2261,7 +2261,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>26</v>
       </c>
@@ -2317,7 +2317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>26</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>26</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="37">
         <v>2022</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>7.48</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>26</v>
       </c>
@@ -2539,7 +2539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
@@ -2595,7 +2595,7 @@
         <v>7.48</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>26</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="39">
         <v>2021</v>
       </c>
@@ -2705,7 +2705,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>26</v>
       </c>
@@ -2761,7 +2761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>26</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>26</v>
       </c>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="37">
         <v>2020</v>
       </c>
@@ -2927,7 +2927,7 @@
         <v>2.09</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>26</v>
       </c>
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>26</v>
       </c>
@@ -3039,7 +3039,7 @@
         <v>2.09</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2019</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>3.32</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>26</v>
       </c>
@@ -3149,7 +3149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>26</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>3.32</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="37">
         <v>2018</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>6.93</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="39">
         <v>2017</v>
       </c>
@@ -3313,7 +3313,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2016</v>
       </c>
@@ -3367,7 +3367,7 @@
         <v>6.08</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="39">
         <v>2015</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>7.26</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>2014</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>4.91</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="39">
         <v>2013</v>
       </c>
@@ -3529,7 +3529,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="37">
         <v>2012</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="39">
         <v>2011</v>
       </c>
@@ -3637,7 +3637,7 @@
         <v>6.34</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="37">
         <v>2010</v>
       </c>
@@ -3691,7 +3691,7 @@
         <v>4.82</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="39">
         <v>2009</v>
       </c>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="37">
         <v>2008</v>
       </c>
@@ -3799,7 +3799,7 @@
         <v>5.44</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="39">
         <v>2007</v>
       </c>
@@ -3853,7 +3853,7 @@
         <v>5.14</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="37">
         <v>2006</v>
       </c>
@@ -3907,7 +3907,7 @@
         <v>6.64</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="39">
         <v>2005</v>
       </c>
@@ -3961,7 +3961,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="37">
         <v>2004</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>2.57</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="39">
         <v>2003</v>
       </c>
@@ -4069,7 +4069,7 @@
         <v>3.64</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="37">
         <v>2002</v>
       </c>
@@ -4123,7 +4123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="39">
         <v>2001</v>
       </c>
@@ -4177,7 +4177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="37">
         <v>2000</v>
       </c>
@@ -4231,7 +4231,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="39">
         <v>1999</v>
       </c>
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="37">
         <v>1998</v>
       </c>
@@ -4339,7 +4339,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="39">
         <v>1997</v>
       </c>
@@ -4393,7 +4393,7 @@
         <v>5.42</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="37">
         <v>1996</v>
       </c>
@@ -4447,7 +4447,7 @@
         <v>5.57</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="39">
         <v>1995</v>
       </c>
@@ -4501,7 +4501,7 @@
         <v>7.26</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="37">
         <v>1994</v>
       </c>
@@ -4555,7 +4555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="39">
         <v>1993</v>
       </c>
@@ -4609,7 +4609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="37">
         <v>1992</v>
       </c>
@@ -4663,7 +4663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="39">
         <v>1991</v>
       </c>
@@ -4717,7 +4717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="37">
         <v>1990</v>
       </c>
@@ -4771,7 +4771,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="39">
         <v>1988</v>
       </c>
@@ -4825,7 +4825,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="37">
         <v>1987</v>
       </c>
@@ -4879,7 +4879,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="39">
         <v>1985</v>
       </c>
@@ -4933,7 +4933,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="37">
         <v>1984</v>
       </c>
@@ -4987,7 +4987,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="39" t="s">
         <v>46</v>
       </c>
